--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,6 +1134,125 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128806789</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92374</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Basevad, mossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484103</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6323501</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Mosse med tall</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Dikad högmosse med tall.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92406</v>
+        <v>92411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92411</v>
+        <v>92415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92415</v>
+        <v>92420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92428</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92436</v>
+        <v>92443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92443</v>
+        <v>92450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92450</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>128806789</v>
       </c>
       <c r="B6" t="n">
-        <v>92466</v>
+        <v>92467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>132147102</v>
       </c>
       <c r="B7" t="n">
-        <v>57869</v>
+        <v>57870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>132147102</v>
       </c>
       <c r="B7" t="n">
-        <v>57870</v>
+        <v>57874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>132147102</v>
       </c>
       <c r="B7" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>133352435</v>
       </c>
       <c r="B8" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>133352464</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>133352448</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>133352435</v>
       </c>
       <c r="B8" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>133352464</v>
       </c>
       <c r="B9" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>133352448</v>
       </c>
       <c r="B10" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -675,51 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111325650</v>
+        <v>116118699</v>
       </c>
       <c r="B2" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484177.3247218406</v>
+        <v>484177</v>
       </c>
       <c r="R2" t="n">
-        <v>6323635.040671465</v>
+        <v>6323635</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -757,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,47 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113689362</v>
+        <v>128806789</v>
       </c>
       <c r="B3" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>4745</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +823,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484177</v>
+        <v>484103</v>
       </c>
       <c r="R3" t="n">
-        <v>6323635</v>
+        <v>6323501</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,8 +867,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Mosse med tall</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Dikad högmosse med tall.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,45 +896,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113688722</v>
+        <v>132147102</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -997,12 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116118699</v>
+        <v>133352448</v>
       </c>
       <c r="B5" t="n">
-        <v>94512</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,27 +1030,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484177</v>
+        <v>484103</v>
       </c>
       <c r="R5" t="n">
-        <v>6323635</v>
+        <v>6323501</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,12 +1096,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1120,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1136,45 +1138,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128806789</v>
+        <v>113688722</v>
       </c>
       <c r="B6" t="n">
-        <v>92467</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484103</v>
+        <v>484177</v>
       </c>
       <c r="R6" t="n">
-        <v>6323501</v>
+        <v>6323635</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,12 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,19 +1225,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Mosse med tall</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Dikad högmosse med tall.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,48 +1243,40 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132147102</v>
+        <v>133352464</v>
       </c>
       <c r="B7" t="n">
-        <v>57875</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1306,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484177</v>
+        <v>484103</v>
       </c>
       <c r="R7" t="n">
-        <v>6323635</v>
+        <v>6323501</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,22 +1316,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,44 +1358,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133352435</v>
+        <v>113689362</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1425,13 +1401,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484103</v>
+        <v>484177</v>
       </c>
       <c r="R8" t="n">
-        <v>6323501</v>
+        <v>6323635</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,22 +1431,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,40 +1473,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133352464</v>
+        <v>111325650</v>
       </c>
       <c r="B9" t="n">
-        <v>57162</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1540,13 +1520,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484103</v>
+        <v>484177</v>
       </c>
       <c r="R9" t="n">
-        <v>6323501</v>
+        <v>6323635</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,22 +1550,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133352448</v>
+        <v>133352435</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,21 +1593,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116118699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128806789</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132147102</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133352448</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113688722</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133352464</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113689362</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111325650</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,8 +1743,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133352435</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>